--- a/results/att_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/att_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.043</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.061</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.057</v>
+        <v>0.045</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -672,7 +672,7 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0.008999999999999999</v>
@@ -699,10 +699,10 @@
         <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -834,10 +834,10 @@
         <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -861,10 +861,10 @@
         <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -888,10 +888,10 @@
         <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -915,10 +915,10 @@
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -969,10 +969,10 @@
         <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -996,10 +996,10 @@
         <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1131,10 +1131,10 @@
         <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1293,10 +1293,10 @@
         <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1388,13 +1388,13 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>554.8407173044708</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07201647252918561</v>
+        <v>0.07201588164977409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2496220969064754</v>
+        <v>0.2496221955703657</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.147612970200426</v>
+        <v>2.036602236209994</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3505792626689341</v>
+        <v>0.3595551986980739</v>
       </c>
       <c r="D2" t="n">
-        <v>1.460490241642707</v>
+        <v>1.331886996307626</v>
       </c>
       <c r="E2" t="n">
-        <v>2.834735698758144</v>
+        <v>2.741317476112362</v>
       </c>
       <c r="F2" t="n">
-        <v>9.017329355926007e-10</v>
+        <v>1.476888557170508e-08</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05845161905252275</v>
+        <v>-0.06313566390614946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07160092997972564</v>
+        <v>0.06889171256433491</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1987868630723592</v>
+        <v>-0.1981609393655314</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08188362496731375</v>
+        <v>0.07188961155323249</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4142983889000481</v>
+        <v>0.3594320324412417</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1312227401028711</v>
+        <v>-0.1420900222427462</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1641582199693825</v>
+        <v>0.1674834691504836</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4529669390090647</v>
+        <v>-0.4703515897835193</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1905214588033225</v>
+        <v>0.1861715452980268</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4240773701622703</v>
+        <v>0.3962250586520983</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1033551762074399</v>
+        <v>0.1123402147235629</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1319544707330703</v>
+        <v>0.1386455160915384</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1552708340284226</v>
+        <v>-0.159400003433821</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3619811864433022</v>
+        <v>0.3840804328809467</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4334721449890785</v>
+        <v>0.4177853765636298</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2478856342882237</v>
+        <v>0.2616157459576962</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1454889655325324</v>
+        <v>0.1491654091054351</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03726749830352913</v>
+        <v>-0.03074308362813966</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5330387668799764</v>
+        <v>0.5539745755435321</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08841648649044939</v>
+        <v>0.07945392276127165</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2138498188815498</v>
+        <v>0.2268721888728757</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1325550674075284</v>
+        <v>0.1322971139673636</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04595333920548508</v>
+        <v>-0.03242538976174789</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4736529769685847</v>
+        <v>0.4861697675074992</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1066814293264166</v>
+        <v>0.08636928988307642</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2761216398872336</v>
+        <v>0.2700551131784785</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1538647751149888</v>
+        <v>0.1556352113937796</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02544777782749924</v>
+        <v>-0.0349842958796075</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5776910576019665</v>
+        <v>0.5750945222365644</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07272168683587071</v>
+        <v>0.08270891977837912</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03656220084389578</v>
+        <v>0.05428434711663997</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1217553030857</v>
+        <v>0.125676157999888</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2020738081308346</v>
+        <v>-0.1920363962785059</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2751982098186262</v>
+        <v>0.3006050905117859</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7639540755168462</v>
+        <v>0.6657862511070218</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.278752363381223</v>
+        <v>0.2497052052682608</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1802539830636219</v>
+        <v>0.181310392693877</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.07453895149336875</v>
+        <v>-0.1056566344345522</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6320436782558148</v>
+        <v>0.6050670449710738</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1219978128054395</v>
+        <v>0.1684426953271448</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0336168978535344</v>
+        <v>-0.0540618249941116</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2012828326149305</v>
+        <v>0.2032970913516045</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4281240004850023</v>
+        <v>-0.4525168022050057</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3608902047779335</v>
+        <v>0.3443931522167825</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8673596319272416</v>
+        <v>0.7902967967088373</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2130446379476058</v>
+        <v>0.1958077105120103</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1515209272806089</v>
+        <v>0.1454915101622128</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.08393092242650016</v>
+        <v>-0.08935040946227002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5100201983217117</v>
+        <v>0.4809658304862906</v>
       </c>
       <c r="F12" t="n">
-        <v>0.159711946797643</v>
+        <v>0.1783554160232428</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2738364591796319</v>
+        <v>0.2559736583242182</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1734619876470114</v>
+        <v>0.1734212677168906</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06614278929524225</v>
+        <v>-0.08392578055416605</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6138157076545061</v>
+        <v>0.5958730972026025</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1144154432496022</v>
+        <v>0.1399379060136733</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2822352547979426</v>
+        <v>0.2621085393999599</v>
       </c>
       <c r="C14" t="n">
-        <v>0.165770592894802</v>
+        <v>0.1613185653416906</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.04266913697172064</v>
+        <v>-0.05407003870742511</v>
       </c>
       <c r="E14" t="n">
-        <v>0.607139646567606</v>
+        <v>0.578287117507345</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08864945347485848</v>
+        <v>0.1042076460090703</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1318046761001984</v>
+        <v>0.1217698113596891</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1766931593292863</v>
+        <v>0.1773010282590539</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2145075524998003</v>
+        <v>-0.225733818449975</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4781169047001971</v>
+        <v>0.4692734411693531</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4556962044894306</v>
+        <v>0.4922106710207486</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07056390915964809</v>
+        <v>-0.09452849173092542</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1703937053037507</v>
+        <v>0.1774418821294872</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4045294347473311</v>
+        <v>-0.4423081900537217</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2634016164280349</v>
+        <v>0.2532512065918708</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6787842153424423</v>
+        <v>0.5942209726114982</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2264779557962663</v>
+        <v>0.1837143702306888</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1686475038455734</v>
+        <v>0.1637040102408051</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1040650778236379</v>
+        <v>-0.1371395939660655</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5570209894161705</v>
+        <v>0.5045683344274431</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1793020082079895</v>
+        <v>0.2617625340704767</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0760264389200066</v>
+        <v>-0.0698174838724764</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2013049674445815</v>
+        <v>0.1930840620841171</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4705769250203944</v>
+        <v>-0.4482552915460417</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3185240471803812</v>
+        <v>0.3086203238010889</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7056772628911938</v>
+        <v>0.7176575952681568</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2099732755893716</v>
+        <v>0.1969655303245182</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1804005455208353</v>
+        <v>0.1779209025639871</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1436052964228441</v>
+        <v>-0.1517530307977566</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5635518476015873</v>
+        <v>0.5456840914467931</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2444531251926898</v>
+        <v>0.2682766969715215</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1629385619778168</v>
+        <v>0.1322032620606824</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1723465012757394</v>
+        <v>0.1728217080449773</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1748543733841189</v>
+        <v>-0.2065210614541693</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5007314973397526</v>
+        <v>0.470927585575534</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3444482479859423</v>
+        <v>0.4442899600438315</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1502454725345474</v>
+        <v>0.1411989312213751</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1543574410114696</v>
+        <v>0.1536032454395491</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1522895525936988</v>
+        <v>-0.1598578977486074</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4527804976627936</v>
+        <v>0.4422557601913576</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3303740456209944</v>
+        <v>0.3579677249886004</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.002506259866841104</v>
+        <v>-0.03228862083243174</v>
       </c>
       <c r="C22" t="n">
-        <v>0.174422579094368</v>
+        <v>0.170009690823173</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3443682329823914</v>
+        <v>-0.3655014918686405</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3393557132487092</v>
+        <v>0.3009242502037771</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9885356743718703</v>
+        <v>0.8493700668133847</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2541793268758947</v>
+        <v>0.252857861521117</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1702294552629513</v>
+        <v>0.170788251243906</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.07946427454736216</v>
+        <v>-0.08188095989951694</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5878229282991516</v>
+        <v>0.5875966829417509</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1353960578127335</v>
+        <v>0.1387307179459427</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09216186183899398</v>
+        <v>0.1009814874983657</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1157771107851795</v>
+        <v>0.1174236802772658</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1347571055340618</v>
+        <v>-0.1291646967772215</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3190808292120498</v>
+        <v>0.3311276717739529</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4260155607133016</v>
+        <v>0.3898025510379961</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.01171966964763415</v>
+        <v>0.004330053901152274</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08401433574445505</v>
+        <v>0.08182631997408589</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1763847418918222</v>
+        <v>-0.1560465862355065</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1529454025965538</v>
+        <v>0.164706694037811</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8890581613806194</v>
+        <v>0.9577975473342347</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.04287673788326097</v>
+        <v>-0.05122561371632545</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1027742983851172</v>
+        <v>0.1055959012379954</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2443106612544636</v>
+        <v>-0.2581897770578449</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1585571854879417</v>
+        <v>0.155738549625194</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6765371024288969</v>
+        <v>0.6275984125035594</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1001773642437923</v>
+        <v>-0.1108286684308805</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1121717979826482</v>
+        <v>0.1140937462761549</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3200300483708855</v>
+        <v>-0.334448301993395</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1196753198833009</v>
+        <v>0.112790965131634</v>
       </c>
       <c r="F27" t="n">
-        <v>0.371819226150534</v>
+        <v>0.3313578400077098</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.235942960035484e-05</v>
+        <v>-0.0122039672480043</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1120175198091301</v>
+        <v>0.118018522902887</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2194979450337967</v>
+        <v>-0.2435160216462784</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2196026638929975</v>
+        <v>0.2191080871502698</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9996270513841005</v>
+        <v>0.9176397829023986</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09390885156219439</v>
+        <v>0.09048136114066339</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1054691865571917</v>
+        <v>0.1120837691629426</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1128069555686373</v>
+        <v>-0.1291987896702052</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3006246586930261</v>
+        <v>0.310161511951532</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3732557845936563</v>
+        <v>0.4195135299990495</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.04660944779469506</v>
+        <v>-0.04579550992862554</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0397320753594812</v>
+        <v>0.0390974269238365</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1244828845303095</v>
+        <v>-0.1224250585875317</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03126398894091942</v>
+        <v>0.03083403873028063</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2407582275589254</v>
+        <v>0.2414710814149404</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.461215227127711</v>
+        <v>-0.02241147003507635</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03570737034211655</v>
+        <v>0.01594802218291605</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3912300672745289</v>
+        <v>-0.05366901913823766</v>
       </c>
       <c r="E31" t="n">
-        <v>0.531200386980893</v>
+        <v>0.008846079068084958</v>
       </c>
       <c r="F31" t="n">
-        <v>3.631653095325903e-38</v>
+        <v>0.1599374102620151</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004892683507390617</v>
+        <v>0.4536514594486489</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005337959351310919</v>
+        <v>0.03633543277518648</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.01535489158689881</v>
+        <v>0.3824353198466071</v>
       </c>
       <c r="E32" t="n">
-        <v>0.005569524572117575</v>
+        <v>0.5248675990506906</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3593611261096166</v>
+        <v>9.003178021310825e-36</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001269465397345405</v>
+        <v>0.005570573422178937</v>
       </c>
       <c r="C33" t="n">
-        <v>0.005712194484502108</v>
+        <v>0.00500659875732285</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01246516085965788</v>
+        <v>-0.004242179827216838</v>
       </c>
       <c r="E33" t="n">
-        <v>0.009926230064967066</v>
+        <v>0.01538332667157471</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8241287884464616</v>
+        <v>0.265860380906523</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01030563244109419</v>
+        <v>-0.009996935471112973</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006131426736497234</v>
+        <v>0.006231431833130051</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.02232300801847473</v>
+        <v>-0.02221031743616428</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001711743136286348</v>
+        <v>0.002216446493938335</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0928039748473348</v>
+        <v>0.1086532664978433</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.01845286638953105</v>
+        <v>-0.0009841142683511327</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07679201423705706</v>
+        <v>0.005676324387152112</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.16896244859445</v>
+        <v>-0.01210950563173567</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1320567158153879</v>
+        <v>0.0101412770950334</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8101002653924934</v>
+        <v>0.8623592324210251</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.01463224491046515</v>
+        <v>-0.01832790500755674</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01540079412387663</v>
+        <v>0.07641092741851573</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.04481724672657943</v>
+        <v>-0.1680905707731517</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01555275690564913</v>
+        <v>0.1314347607580382</v>
       </c>
       <c r="F36" t="n">
-        <v>0.342063079077078</v>
+        <v>0.8104389944348601</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.350970771285248</v>
+        <v>-2.68060017980294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4605522587714034</v>
+        <v>0.4771933030981267</v>
       </c>
       <c r="D2" t="n">
-        <v>3.313590542287848e-07</v>
+        <v>1.93818176827037e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02128055977478192</v>
+        <v>-0.02542074333516159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09751395156308111</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.827249191641336</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2245966634275915</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2329354389845562</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3349449904957182</v>
+        <v>0.3364439424069164</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8167052829997485</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1617156577703267</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>4.412210487480358e-07</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03599538577094948</v>
+        <v>0.03527526670387294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1898688322218615</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8496380437366924</v>
+        <v>0.8539945454713553</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2765708211818085</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1824472225347018</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.129545920374235</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1102648615599912</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1853641405651108</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519401263365121</v>
+        <v>0.5954095400432468</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8745743640527194</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1615402513662274</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>6.164188141358052e-08</v>
+        <v>2.539495077342719e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04349724922704642</v>
+        <v>-0.04456520772617057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2655215602978132</v>
+        <v>0.2604021031716314</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8698743077153893</v>
+        <v>0.8641137091517844</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2685655156863916</v>
+        <v>-0.2737623724798145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2761865361461748</v>
+        <v>0.2787881385465063</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3308484806726052</v>
+        <v>0.3261132423877634</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08406558527820192</v>
+        <v>0.08100487957118158</v>
       </c>
       <c r="C12" t="n">
-        <v>0.251020166800007</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7377037334343584</v>
+        <v>0.7550514391424689</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04159103469582721</v>
+        <v>0.03917827337461771</v>
       </c>
       <c r="C13" t="n">
-        <v>0.255561465250315</v>
+        <v>0.2572958805743772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8707201879025983</v>
+        <v>0.8789745077123736</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05097157642059893</v>
+        <v>-0.05296103812307912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2615504699624188</v>
+        <v>0.2610089865588722</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8454850334004391</v>
+        <v>0.8392062624375538</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1235593461635321</v>
+        <v>0.1181322726534163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2569613848518211</v>
+        <v>0.2572294350577189</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6306245929938302</v>
+        <v>0.6460556128984085</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002490750131026257</v>
+        <v>-0.00400098624037939</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2457746491930773</v>
+        <v>0.2383903410311194</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9919141495524532</v>
+        <v>0.9866094604655136</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1110262478895003</v>
+        <v>0.1057185310395308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2594324060220158</v>
+        <v>0.2543340222421757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6686814903924607</v>
+        <v>0.6776529122567302</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1338440250599403</v>
+        <v>-0.1377694895733253</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2694490717592011</v>
+        <v>0.2636874203313639</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6193779257550096</v>
+        <v>0.6013412201546287</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02068301206114321</v>
+        <v>-0.0255715409422322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2629683391871477</v>
+        <v>0.2527597901538112</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9373093461992266</v>
+        <v>0.9194160355966682</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0686991433762508</v>
+        <v>-0.07344622569376394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2617458461247386</v>
+        <v>0.2674578609541013</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7929629071620667</v>
+        <v>0.7836169672222786</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2112158738988716</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2400889859196068</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3790001987958982</v>
+        <v>0.3983578134719856</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.159933319308369</v>
+        <v>-0.1704634573362025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2649283257747139</v>
+        <v>0.2696748454965907</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5460529306471213</v>
+        <v>0.5273167196806369</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4920005620651325</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2884409459397611</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08805953197431808</v>
+        <v>0.08105838975171867</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9425285809878476</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1559773650465781</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>1.515312581506736e-09</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5768512495314141</v>
+        <v>-0.5776106069409676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1130405709043027</v>
+        <v>0.1143619392421805</v>
       </c>
       <c r="D25" t="n">
-        <v>3.342294640071132e-07</v>
+        <v>4.401383208103756e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2384858887162336</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1457315480836286</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1017404238903948</v>
+        <v>0.1145360411757809</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04585234373593617</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1593109532353293</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7734870970055308</v>
+        <v>0.7872365295400219</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07857740431296747</v>
+        <v>-0.07514354096975731</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1565335672967476</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6156785148897228</v>
+        <v>0.6414556246120153</v>
       </c>
     </row>
     <row r="29">
@@ -2807,45 +2807,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09755305493394664</v>
+        <v>0.09749293462742098</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1499487653516257</v>
+        <v>0.1543265796290168</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5153202832397639</v>
+        <v>0.5275624553510017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.006860378637723895</v>
+        <v>-0.004129656026475424</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006945236405256705</v>
+        <v>0.02222260881033181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3232594861617505</v>
+        <v>0.8525770672961283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002646425713821547</v>
+        <v>0.006335499136474501</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007095424075339026</v>
+        <v>0.006871422968197188</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7091660102282209</v>
+        <v>0.3565249957666434</v>
       </c>
     </row>
     <row r="32">
@@ -2855,45 +2855,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004895000819746557</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008684655396149939</v>
+        <v>0.008304876992454852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5730005966817302</v>
+        <v>0.5461741835341496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2261835420647834</v>
+        <v>-0.00241813341219285</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1139281184793711</v>
+        <v>0.007135781003458538</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04710910483736543</v>
+        <v>0.7347043603418298</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01540023496026497</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0213723694247541</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D34" t="n">
-        <v>0.47117565131408</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
   </sheetData>
